--- a/Skill问题记录.xlsx
+++ b/Skill问题记录.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7990"/>
+    <workbookView windowWidth="19200" windowHeight="7240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>编号</t>
   </si>
@@ -124,6 +124,21 @@
   </si>
   <si>
     <t>增加输入信息的要求</t>
+  </si>
+  <si>
+    <t>0006</t>
+  </si>
+  <si>
+    <t>衔接问题</t>
+  </si>
+  <si>
+    <t>确认候选开头后重复确认开头</t>
+  </si>
+  <si>
+    <t>繁琐的一步</t>
+  </si>
+  <si>
+    <t>直接在确认候选开头后，写正文并给核心观点及写作思路</t>
   </si>
 </sst>
 </file>
@@ -1191,13 +1206,28 @@
       </c>
     </row>
     <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F5:F7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7">
       <formula1>"待修改,已解决"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Skill问题记录.xlsx
+++ b/Skill问题记录.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
   <si>
     <t>编号</t>
   </si>
@@ -138,7 +138,58 @@
     <t>繁琐的一步</t>
   </si>
   <si>
-    <t>直接在确认候选开头后，写正文并给核心观点及写作思路</t>
+    <t>直接在确认候选开头后，写正文并给核心观点及写作思路，不再重新选择观点等</t>
+  </si>
+  <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>交接问题</t>
+  </si>
+  <si>
+    <t>第3节第5步只是提醒用户提供信息，没有标准交接模板</t>
+  </si>
+  <si>
+    <t>需要用户自行复制粘贴，较麻烦</t>
+  </si>
+  <si>
+    <t>增加最终交接稿，或者在前面步骤输出时就带上定稿</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>没有处理未读取到前文结果的情况</t>
+  </si>
+  <si>
+    <t>如果换对话窗口或模型不处理，则无法正常生成正文</t>
+  </si>
+  <si>
+    <t>开头部分增加调用过程，正文部分增加衔接过程</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>结尾要求不清晰</t>
+  </si>
+  <si>
+    <t>没有规则就无法判断是否达到要求</t>
+  </si>
+  <si>
+    <t>明确结尾数量、句式和作用、及是否与全文一致</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>正文可能补充未验证事实</t>
+  </si>
+  <si>
+    <t>不符合事实容易违规</t>
+  </si>
+  <si>
+    <t>正文skill必填输入：可使用的事实信息，要验证是否属实，缺信息时询问</t>
   </si>
 </sst>
 </file>
@@ -1072,8 +1123,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="11.4545454545455" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
@@ -1225,9 +1276,149 @@
         <v>12</v>
       </c>
     </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6">
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6">
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6">
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6">
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6">
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6">
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F23">
       <formula1>"待修改,已解决"</formula1>
     </dataValidation>
   </dataValidations>
